--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487951_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487951_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0331</v>
+        <v>6.8252</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4587</v>
+        <v>6.4192</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5744</v>
+        <v>0.4059</v>
       </c>
       <c r="G2" t="n">
         <v>2.7622</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4603</v>
+        <v>0.2523</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0369</v>
+        <v>-0.0026</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4234</v>
+        <v>0.2549</v>
       </c>
       <c r="V2" t="n">
         <v>3.0178</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>J. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2012</v>
+        <v>3.275</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6547</v>
+        <v>3.3627</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5465</v>
+        <v>-0.0877</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2164</v>
+        <v>1.2326</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.066</v>
+        <v>0.1919</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2823</v>
+        <v>1.0407</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0395</v>
+        <v>3.7965</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3839</v>
+        <v>1.1772</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6556</v>
+        <v>2.6193</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8232</v>
+        <v>-2.5639</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4499</v>
+        <v>-0.9853</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3733</v>
+        <v>-1.5786</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7929</v>
+        <v>2.7751</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1805</v>
+        <v>2.7751</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3259</v>
+        <v>-0.4662</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1367</v>
+        <v>-0.4339</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1892</v>
+        <v>-0.0323</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5482</v>
+        <v>-0.2666</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.5482</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTIN GONZALEZ</t>
+          <t>A. BUALÓ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4443</v>
+        <v>2.416</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7286</v>
+        <v>2.416</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2843</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2326</v>
+        <v>2.416</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1919</v>
+        <v>1.2107</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0407</v>
+        <v>1.2053</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7965</v>
+        <v>2.416</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1772</v>
+        <v>1.2107</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6193</v>
+        <v>1.2053</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5639</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9853</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5786</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7751</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7751</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2969</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.068</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2289</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BUALÓ</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.416</v>
+        <v>1.7251</v>
       </c>
       <c r="E5" t="n">
-        <v>2.416</v>
+        <v>0.2909</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.4342</v>
       </c>
       <c r="G5" t="n">
-        <v>2.416</v>
+        <v>2.2164</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2107</v>
+        <v>-0.066</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2053</v>
+        <v>2.2823</v>
       </c>
       <c r="J5" t="n">
-        <v>2.416</v>
+        <v>3.0395</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2107</v>
+        <v>0.3839</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2053</v>
+        <v>2.6556</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.8232</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.4499</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.3733</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.8498</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.7729</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5482</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.5482</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2032</v>
+        <v>1.3393</v>
       </c>
       <c r="E6" t="n">
-        <v>1.179</v>
+        <v>1.3433</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0241</v>
+        <v>-0.0039</v>
       </c>
       <c r="G6" t="n">
         <v>0.9099</v>
@@ -922,13 +922,13 @@
         <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1032</v>
+        <v>0.033</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1872</v>
+        <v>-0.0229</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0559</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1818</v>
+        <v>0.5808</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1008</v>
+        <v>-0.3648</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2826</v>
+        <v>0.9457</v>
       </c>
       <c r="G7" t="n">
         <v>0.6084000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>2.7751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2284</v>
+        <v>0.1706</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8184</v>
+        <v>-0.0824</v>
       </c>
       <c r="U7" t="n">
-        <v>0.59</v>
+        <v>0.253</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1059</v>
+        <v>-0.1997</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4104</v>
+        <v>0.1048</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3045</v>
@@ -1078,10 +1078,10 @@
         <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2093</v>
+        <v>-0.0964</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3782</v>
+        <v>0.0726</v>
       </c>
       <c r="U8" t="n">
         <v>-0.1689</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANCHEZ</t>
+          <t>M. PEREZ SARRABLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4154</v>
+        <v>-1.0282</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0422</v>
+        <v>0.3679</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3732</v>
+        <v>-1.3961</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5153</v>
+        <v>0.633</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5153</v>
+        <v>1.1649</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.5319</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0202</v>
+        <v>3.4957</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0202</v>
+        <v>2.1659</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.3298</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5355</v>
+        <v>-2.8627</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5355</v>
+        <v>-1.001</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-1.8617</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2966</v>
+        <v>-0.5313</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0624</v>
+        <v>-0.4716</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2342</v>
+        <v>-0.0597</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6036</v>
+        <v>-0.337</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6036</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. PEREZ SARRABLO</t>
+          <t>J. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5471</v>
+        <v>-1.3593</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1017</v>
+        <v>-0.0422</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6488</v>
+        <v>-1.3171</v>
       </c>
       <c r="G10" t="n">
-        <v>0.633</v>
+        <v>-0.5153</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1649</v>
+        <v>-0.5153</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5319</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4957</v>
+        <v>0.0202</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1659</v>
+        <v>0.0202</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3298</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8627</v>
+        <v>-0.5355</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.001</v>
+        <v>-0.5355</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8617</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0502</v>
+        <v>-0.2405</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7377</v>
+        <v>-0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3124</v>
+        <v>-0.1781</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.337</v>
+        <v>-0.6036</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.337</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0581</v>
+        <v>-1.4479</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5345</v>
+        <v>-2.0647</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4764</v>
+        <v>0.6168</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7709</v>
@@ -1312,13 +1312,13 @@
         <v>2.3787</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1068</v>
+        <v>-0.4965</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7046</v>
+        <v>-0.2348</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4021</v>
+        <v>-0.2617</v>
       </c>
       <c r="V11" t="n">
         <v>2.4142</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2033</v>
+        <v>-2.1409</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0284</v>
+        <v>-0.966</v>
       </c>
       <c r="F12" t="n">
         <v>-1.1749</v>
@@ -1390,10 +1390,10 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5836</v>
+        <v>-0.5212</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5505</v>
+        <v>-0.4881</v>
       </c>
       <c r="U12" t="n">
         <v>-0.0331</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.361600000000001</v>
+        <v>9.985399999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>10.2432</v>
+        <v>10.8671</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8817000000000004</v>
+        <v>-0.8815999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2.716600000000002</v>
+        <v>2.7166</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0374</v>
+        <v>2.037400000000001</v>
       </c>
       <c r="I13" t="n">
         <v>0.6790000000000005</v>
@@ -1444,10 +1444,10 @@
         <v>17.4969</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6235</v>
+        <v>7.623500000000002</v>
       </c>
       <c r="L13" t="n">
-        <v>9.873400000000002</v>
+        <v>9.8734</v>
       </c>
       <c r="M13" t="n">
         <v>-14.7804</v>
@@ -1468,13 +1468,13 @@
         <v>15.8578</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6702</v>
+        <v>-1.0464</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.577</v>
+        <v>-0.9531999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09300000000000005</v>
+        <v>-0.09309999999999996</v>
       </c>
       <c r="V13" t="n">
         <v>4.3506</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2218</v>
+        <v>3.8905</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8253</v>
+        <v>3.3347</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3964</v>
+        <v>0.5558</v>
       </c>
       <c r="G14" t="n">
         <v>2.048</v>
@@ -1546,13 +1546,13 @@
         <v>0.9911</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2952</v>
+        <v>0.3735</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5395</v>
+        <v>-0.0302</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2443</v>
+        <v>0.4037</v>
       </c>
       <c r="V14" t="n">
         <v>0.4778</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4726</v>
+        <v>3.4972</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7894</v>
+        <v>4.2988</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3168</v>
+        <v>-0.8016</v>
       </c>
       <c r="G15" t="n">
         <v>2.7851</v>
@@ -1624,13 +1624,13 @@
         <v>1.1893</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5107</v>
+        <v>0.5139</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7781</v>
+        <v>-0.2687</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2674</v>
+        <v>0.7826</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. LIBERATORE DARGAM</t>
+          <t>A. KRASTS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1139</v>
+        <v>2.7801</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1218</v>
+        <v>1.0748</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.7052</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0592</v>
+        <v>2.9741</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0286</v>
+        <v>0.8179</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0306</v>
+        <v>2.1561</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9287</v>
+        <v>2.9509</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1614</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7673</v>
+        <v>2.0089</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9879</v>
+        <v>0.0232</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.19</v>
+        <v>-0.1241</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.1472</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S16" t="n">
-        <v>1.845</v>
+        <v>0.0835</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1931</v>
+        <v>-0.211</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6518</v>
+        <v>0.2945</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2666</v>
+        <v>-0.674</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. KRASTS</t>
+          <t>M. LIBERATORE DARGAM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9723</v>
+        <v>1.5262</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8711</v>
+        <v>1.5106</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1012</v>
+        <v>0.0156</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9741</v>
+        <v>-0.0592</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8179</v>
+        <v>-0.0286</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1561</v>
+        <v>-0.0306</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9509</v>
+        <v>0.9287</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.1614</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0089</v>
+        <v>0.7673</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0232</v>
+        <v>-0.9879</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1241</v>
+        <v>-0.19</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1472</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7243000000000001</v>
+        <v>1.2573</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4147</v>
+        <v>0.5819</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3095</v>
+        <v>0.6753</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.674</v>
+        <v>-0.2666</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2082</v>
+        <v>0.4459</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4161</v>
+        <v>2.518</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2079</v>
+        <v>-2.0721</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9149</v>
@@ -1858,13 +1858,13 @@
         <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6057</v>
+        <v>0.8434</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3268</v>
+        <v>0.4287</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2789</v>
+        <v>0.4147</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8701</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CORTES ANDRADES</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2889</v>
+        <v>-0.4329</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.305</v>
+        <v>2.4875</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0161</v>
+        <v>-2.9204</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8807</v>
+        <v>2.3144</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8366</v>
+        <v>-2.1723</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0441</v>
+        <v>4.4867</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5584</v>
+        <v>5.022</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6388</v>
+        <v>-0.9074</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0804</v>
+        <v>5.9295</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3223</v>
+        <v>-2.7076</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1979</v>
+        <v>-1.2648</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1244</v>
+        <v>-1.4428</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7929</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1982</v>
+        <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3847</v>
+        <v>-0.1349</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2445</v>
+        <v>-0.5523</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1402</v>
+        <v>0.4174</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>D. CORTES ANDRADES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7278</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8763</v>
+        <v>-1.0181</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6041</v>
+        <v>0.2081</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3144</v>
+        <v>-0.8807</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1723</v>
+        <v>-0.8366</v>
       </c>
       <c r="I20" t="n">
-        <v>4.4867</v>
+        <v>-0.0441</v>
       </c>
       <c r="J20" t="n">
-        <v>5.022</v>
+        <v>-0.5584</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9074</v>
+        <v>-0.6388</v>
       </c>
       <c r="L20" t="n">
-        <v>5.9295</v>
+        <v>0.0804</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7076</v>
+        <v>-0.3223</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2648</v>
+        <v>-0.1979</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4428</v>
+        <v>-0.1244</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1982</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4298</v>
+        <v>0.8636</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1635</v>
+        <v>0.5314</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2663</v>
+        <v>0.3322</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.068</v>
+        <v>-2.04</v>
       </c>
       <c r="E21" t="n">
         <v>-1.7549</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3132</v>
+        <v>-0.2851</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9709</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1061</v>
+        <v>-0.078</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5526</v>
+        <v>-3.1168</v>
       </c>
       <c r="E22" t="n">
-        <v>0.235</v>
+        <v>-0.3762</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7876</v>
+        <v>-2.7406</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2055</v>
@@ -2170,13 +2170,13 @@
         <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4984</v>
+        <v>0.9342</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8811</v>
+        <v>0.2699</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6173</v>
+        <v>0.6643</v>
       </c>
       <c r="V22" t="n">
         <v>-0.674</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9044</v>
+        <v>-3.1878</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4193</v>
+        <v>-2.0305</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4851</v>
+        <v>-1.1573</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2457</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>0.478</v>
+        <v>0.1946</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4957</v>
+        <v>-0.1155</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0177</v>
+        <v>0.3101</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5331</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7272</v>
+        <v>-4.1454</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3357</v>
+        <v>-4.0301</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3915</v>
+        <v>-0.1153</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3394</v>
@@ -2326,13 +2326,13 @@
         <v>1.3876</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.802</v>
+        <v>-0.2202</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4881</v>
+        <v>-0.1825</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3139</v>
+        <v>-0.0377</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0812</v>
+        <v>-4.3727</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.4386</v>
+        <v>-5.133</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3574</v>
+        <v>0.7603</v>
       </c>
       <c r="G25" t="n">
         <v>-4.2219</v>
@@ -2404,13 +2404,13 @@
         <v>0.7929</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2735</v>
+        <v>0.435</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5395</v>
+        <v>-0.2339</v>
       </c>
       <c r="U25" t="n">
-        <v>0.266</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>0.6036</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.3613</v>
+        <v>-5.965700000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8814999999999991</v>
+        <v>0.8815999999999988</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.243</v>
+        <v>-6.8474</v>
       </c>
       <c r="G26" t="n">
         <v>-2.7166</v>
@@ -2473,7 +2473,7 @@
         <v>-9.8734</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.964500000000001</v>
+        <v>-3.9645</v>
       </c>
       <c r="Q26" t="n">
         <v>-15.8577</v>
@@ -2482,13 +2482,13 @@
         <v>11.8935</v>
       </c>
       <c r="S26" t="n">
-        <v>1.670199999999999</v>
+        <v>5.0659</v>
       </c>
       <c r="T26" t="n">
-        <v>0.09299999999999986</v>
+        <v>0.09299999999999997</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5772</v>
+        <v>4.9728</v>
       </c>
       <c r="V26" t="n">
         <v>-4.3506</v>
